--- a/excel/Skill.xlsx
+++ b/excel/Skill.xlsx
@@ -1,163 +1,162 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr filterPrivacy="true" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="MainSkill" sheetId="1" r:id="rId1"/>
+    <sheet name="MainSkill" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffs</t>
+  </si>
+  <si>
+    <t>shouldMove</t>
+  </si>
+  <si>
+    <t>rageCost</t>
+  </si>
+  <si>
+    <t>audio</t>
   </si>
   <si>
     <t>编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动buff</t>
+  </si>
+  <si>
+    <t>是否需要位移(1:不需要 2：需要）</t>
+  </si>
+  <si>
+    <t>怒气值消耗</t>
+  </si>
+  <si>
+    <t>音效</t>
   </si>
   <si>
     <t>cs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>嘲讽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被动buff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否需要位移(1:不需要 2：需要）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rageCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怒气值消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buffs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shouldMove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>跳劈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>群体治疗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>审时度势</t>
+  </si>
+  <si>
+    <t>wind</t>
   </si>
   <si>
     <t>虎痴撼地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>审时度势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>音效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wind</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>boyHeavyHit1,bladeSlashing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+  </si>
+  <si>
+    <t>lightning</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="300" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="宋体"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <family val="2"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -166,24 +165,49 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="2" borderId="2" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -303,7 +327,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -324,9 +348,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="true"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -347,7 +371,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -376,7 +400,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -385,7 +409,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -394,7 +418,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -417,7 +441,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -443,7 +467,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -471,201 +495,224 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr/>
+  <dimension ref="AA11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="15.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="10"/>
+    <col min="3" max="3" width="15.125" style="10" customWidth="true"/>
+    <col min="4" max="4" width="33.125" style="10" bestFit="true" customWidth="true"/>
+    <col min="5" max="5" width="11" style="10" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="29.375" style="10" bestFit="true" customWidth="true"/>
+    <col min="7" max="26" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4">
+        <v>50</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E7" s="4">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>50</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>50</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>30</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>50</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1">
-        <v>50</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>50</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>50</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>50</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>27</v>
-      </c>
+    <row r="11" spans="6:6">
+      <c r="F11" s="9" t="s"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>